--- a/sample/docs/tabular/premium-register.xlsx
+++ b/sample/docs/tabular/premium-register.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="€#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -470,151 +470,151 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HO-0000001</t>
+          <t>COM-0000005</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Matthew Foster</t>
+          <t>Albano Llopis Hierro</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Homeowners</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2075</v>
+        <v>4485</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HO-0000003</t>
+          <t>HH-0000001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abigail Shaffer</t>
+          <t>Mr. Stewart Montague</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Homeowners</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2023-10-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1610</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PA-0000002</t>
+          <t>HH-0000004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Betty Alvarez</t>
+          <t>Mr. Stewart Montague</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Personal Auto</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1290</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PA-0000004</t>
+          <t>MOT-0000002</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Andrea Young</t>
+          <t>Mr. Stewart Montague</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Personal Auto</t>
+          <t>Motor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1235</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PA-0000005</t>
+          <t>MOT-0000003</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jamie Chavez</t>
+          <t>Yves Traore</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Personal Auto</t>
+          <t>Motor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1360</v>
+        <v>1340</v>
       </c>
     </row>
   </sheetData>

--- a/sample/docs/tabular/premium-register.xlsx
+++ b/sample/docs/tabular/premium-register.xlsx
@@ -470,12 +470,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COM-0000005</t>
+          <t>COM-0000003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Albano Llopis Hierro</t>
+          <t>Dr. Christof Walter B.Sc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,52 +485,52 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>4485</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HH-0000001</t>
+          <t>COM-0000004</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mr. Stewart Montague</t>
+          <t>Wouter Verwoert-Goyaerts van Waderle</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2455</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HH-0000004</t>
+          <t>HH-0000001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -545,16 +545,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2023-10-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2545</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="6">
@@ -590,12 +590,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MOT-0000003</t>
+          <t>MOT-0000005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yves Traore</t>
+          <t>Dr. Christof Walter B.Sc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1340</v>
+        <v>960</v>
       </c>
     </row>
   </sheetData>

--- a/sample/docs/tabular/premium-register.xlsx
+++ b/sample/docs/tabular/premium-register.xlsx
@@ -470,12 +470,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COM-0000003</t>
+          <t>COM-0000001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dr. Christof Walter B.Sc.</t>
+          <t>Mr. Stewart Montague</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,27 +485,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3525</v>
+        <v>5815</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COM-0000004</t>
+          <t>COM-0000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wouter Verwoert-Goyaerts van Waderle</t>
+          <t>Albano Llopis Hierro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -530,31 +530,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HH-0000001</t>
+          <t>COM-0000005</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mr. Stewart Montague</t>
+          <t>Dorit Etzold</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2455</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="6">
@@ -565,7 +565,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mr. Stewart Montague</t>
+          <t>Dott. Alfio Leone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -575,27 +575,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1360</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MOT-0000005</t>
+          <t>MOT-0000004</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dr. Christof Walter B.Sc.</t>
+          <t>Mr. Stewart Montague</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
